--- a/src/attributions/attributions_ig_traj_406.xlsx
+++ b/src/attributions/attributions_ig_traj_406.xlsx
@@ -2137,10 +2137,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06046117823093826</v>
+        <v>0.183120314734378</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.007909739316766725</v>
+        <v>0.01924427862541868</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.03617143756747623</v>
+        <v>-0.1120819941761405</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -2164,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03869436029250251</v>
+        <v>0.2700933386565825</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,67 +2176,67 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01584144556643187</v>
+        <v>-0.03674586720255677</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.06430262375880059</v>
+        <v>-0.1657294250861217</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00200062756105706</v>
+        <v>-0.0108528746024982</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.00263789724914463</v>
+        <v>-0.0247136512414976</v>
       </c>
       <c r="X4" t="n">
-        <v>8.34528595198629e-12</v>
+        <v>-7.51427764887163e-11</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01986167215863759</v>
+        <v>-0.03214379422039576</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.03824757892808039</v>
+        <v>-0.1111350569252021</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.005168229871760966</v>
+        <v>-0.001788437822719912</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
@@ -2245,10 +2245,10 @@
         <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01030283230740666</v>
+        <v>0.09609555909318439</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,52 +2257,52 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01633301706257478</v>
+        <v>-0.05852968020790419</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.02685618701599195</v>
+        <v>-0.1112847689066611</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.07492587708764775</v>
+        <v>0.5161686729891785</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.007006897825721201</v>
+        <v>-0.115966187942206</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.0567577465706859</v>
+        <v>-0.1994701473223698</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.02118179993818275</v>
+        <v>-0.02067043916312052</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,43 +2311,43 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.03479730942526374</v>
+        <v>-0.03939240038352183</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.02496470911223424</v>
+        <v>-0.0631221410683873</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02702503009650351</v>
+        <v>0.09317095193631808</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.002543390464120831</v>
+        <v>0.1098147161109013</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01371765622129902</v>
+        <v>0.134349380988759</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.04767116005597702</v>
+        <v>0.2909202445184311</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,118 +2365,118 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01735994516277115</v>
+        <v>-0.1299472429110717</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.0009443090439617647</v>
+        <v>-0.3088742351128302</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.02567106481714602</v>
+        <v>-0.1443496902292738</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
       </c>
       <c r="CG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.002414153016751877</v>
+        <v>-0.04507965892556801</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.03981135037265942</v>
+        <v>0.1478481633995973</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.009927755335786584</v>
+        <v>-0.172539948233625</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.005147383337092406</v>
+        <v>0.08245379996988524</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.004187654761935099</v>
+        <v>0.09024777874104134</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.01848491243654645</v>
+        <v>-0.1369278374569631</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.009635289768188775</v>
+        <v>-0.0415865134025567</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.04072548189887725</v>
+        <v>0.1388628144076554</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.02772221182754773</v>
+        <v>-0.05454912038267042</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
         <v>-0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01568108709807477</v>
+        <v>-0.1492178829526786</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.08356575704655415</v>
+        <v>0.2078622968333981</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,121 +2485,121 @@
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.01666151858245649</v>
+        <v>-0.05575684360738307</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01649226782566926</v>
+        <v>0.06192495004711659</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.004565776975986806</v>
+        <v>0.1258176316870735</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.004131457518795471</v>
+        <v>0.02850624142362764</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.003328792310246043</v>
+        <v>-0.008593462163998101</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.03499527296410509</v>
+        <v>-0.04569804126004324</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.00475169552876662</v>
+        <v>-0.125679254158566</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.002662632482419291</v>
+        <v>-0.1139021950482049</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.006779651477541583</v>
+        <v>0.06614593700140292</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
         <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.008474771376733036</v>
+        <v>-0.03369420952861728</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.01579659127930758</v>
+        <v>-0.1204885631212082</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.05451194481833147</v>
+        <v>0.1443230476846068</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.02082585527283086</v>
+        <v>-0.1616677069221435</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,25 +2608,25 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.006182685100318832</v>
+        <v>-0.08129015571415472</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03802622771347527</v>
+        <v>0.1320847302570527</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.02038197956518871</v>
+        <v>-0.1527506875991075</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,73 +2635,73 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01954147123197263</v>
+        <v>-0.03191809289646562</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.00756597236182991</v>
+        <v>0.08483113907041676</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.008057711923515334</v>
+        <v>0.06218909433813569</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.008076691247551627</v>
+        <v>0.04803646324727861</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.04782908731962061</v>
+        <v>0.1020245244278432</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.03546251249547273</v>
+        <v>0.01102634768587559</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.008833321501767646</v>
+        <v>0.1338531312689699</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
       </c>
       <c r="GF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,43 +2709,43 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1564027172393281</v>
+        <v>0.1865730257875162</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02891810854352785</v>
+        <v>-0.05708394171339314</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.04395571755856006</v>
+        <v>-0.04039897977743623</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09443164909676101</v>
+        <v>0.1863032451918915</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01664328767877125</v>
+        <v>-0.04485687793988245</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.07617916574702041</v>
+        <v>-0.08472949770911153</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,22 +2760,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0229241764692308</v>
+        <v>0.02523154232371578</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.01091239376204601</v>
+        <v>-0.005794142102986712</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01038140927191501</v>
+        <v>7.198412344723584e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
@@ -2787,79 +2787,79 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0603745988479308</v>
+        <v>-0.02489570443733334</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0159020081734799</v>
+        <v>-0.07266724433410957</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.05997871446106244</v>
+        <v>-0.09212885297821387</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.007822512825865074</v>
+        <v>0.1253097562215067</v>
       </c>
       <c r="AM5" t="n">
         <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.05618511938560545</v>
+        <v>-0.01230194134223813</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.09618447003049881</v>
+        <v>0.08011547057448948</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.322400134801906</v>
+        <v>0.2540525894103609</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.02656766293906415</v>
+        <v>-0.1118055943933746</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1057064648507352</v>
+        <v>-0.1119500974708285</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
         <v>-0</v>
@@ -2871,16 +2871,16 @@
         <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.01579148428392624</v>
+        <v>-0.02029580256628682</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.05855237017317617</v>
+        <v>-0.01255042656590788</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.08703192545830385</v>
+        <v>-0.03490211458424809</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1314020119580843</v>
+        <v>-0.02237313626579126</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.05207982845928911</v>
+        <v>0.04840548328034661</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1804792756881191</v>
+        <v>0.07874954884330103</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,25 +2925,25 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2169878019812399</v>
+        <v>0.261704806066519</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.001982124070230911</v>
+        <v>-0.1339447444912954</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.009279625253152993</v>
+        <v>-0.01328327898497988</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -2952,16 +2952,16 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.06653073678330225</v>
+        <v>-0.1320676331031344</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01750629229039489</v>
+        <v>0.08857617090334961</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.008538558438727259</v>
+        <v>0.02077344641692719</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
@@ -2970,7 +2970,7 @@
         <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
@@ -2979,43 +2979,43 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.01640307587762197</v>
+        <v>-0.0550611244422084</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.01813242171190923</v>
+        <v>0.02743441967654468</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.05595419941434735</v>
+        <v>0.03757359382540939</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
         <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.04291622223219629</v>
+        <v>-0.1398149313639174</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.02736475206348669</v>
+        <v>0.1002055458320874</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0257148550636149</v>
+        <v>0.02868966529716514</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3030,28 +3030,28 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.002272569820687361</v>
+        <v>-0.006250982066762782</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.02404457385877212</v>
+        <v>0.04271137374959527</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.05492666681262005</v>
+        <v>-0.08445690888628317</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
         <v>0</v>
@@ -3060,52 +3060,52 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.08450838710759365</v>
+        <v>-0.06710045939241654</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.004926987592867482</v>
+        <v>0.03912276837708352</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.004185843531745718</v>
+        <v>-0.06929863085180865</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.0003919478747872636</v>
+        <v>0.08788172572612477</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.04117579536394302</v>
+        <v>0.05491671945674567</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.03723351265940349</v>
+        <v>-0.07386414644585525</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,22 +3114,22 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.0485806366544613</v>
+        <v>-0.06893985332069398</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.01435837850429657</v>
+        <v>0.1010173864517867</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.08745810976826489</v>
+        <v>0.01736252127150537</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
@@ -3141,49 +3141,49 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.05143942412615329</v>
+        <v>-0.08998382341677433</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.03025412705260489</v>
+        <v>0.08453358429178712</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.009639112050198146</v>
+        <v>-0.04879225389145241</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.0433450458767879</v>
+        <v>-0.1491364708560312</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.03121425773496929</v>
+        <v>0.1103058554157893</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.03329513894139961</v>
+        <v>0.009237860764798359</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,76 +3192,76 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.05401271203444592</v>
+        <v>-0.04703796057287909</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.06811831900144651</v>
+        <v>-0.005538922117830394</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.01300937069821159</v>
+        <v>0.05782343950296591</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.08011846156680852</v>
+        <v>0.03009071251248189</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.008377038738784027</v>
+        <v>0.1714523326658215</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.03082879734139503</v>
+        <v>-0.07112416759515852</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02598358894243691</v>
+        <v>-0.09750770180652106</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.003814796472217682</v>
+        <v>0.0319861143333105</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02203699579754653</v>
+        <v>0.03735018310544842</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,10 +3287,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.007740480310706088</v>
+        <v>0.02863897609553655</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.002180737468036783</v>
+        <v>-0.00615450393329471</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3305,7 +3305,7 @@
         <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0110376124337492</v>
+        <v>0.07500736952493618</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01474366659191357</v>
+        <v>0.01675191092114212</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01104363029817155</v>
+        <v>-0.02127791433235356</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-5.406574677762423e-05</v>
+        <v>-0.007315004709239832</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,43 +3341,43 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.001808979843718327</v>
+        <v>-0.01109750544703761</v>
       </c>
       <c r="X6" t="n">
-        <v>8.187934304431023e-12</v>
+        <v>7.93971767165408e-13</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01754060513015957</v>
+        <v>-0.02800422144017603</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02340600525096773</v>
+        <v>-0.05429658787611158</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.004715308971651484</v>
+        <v>-0.02828994902049329</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.003817955687453985</v>
+        <v>0.009977422337033269</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,40 +3395,40 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01754160411839323</v>
+        <v>-0.0133523876071088</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.008232216067228092</v>
+        <v>-0.04779896389858076</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.047958667207912</v>
+        <v>0.1245258008988069</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.001638521595537643</v>
+        <v>-0.0190439030786385</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.009488508429564399</v>
+        <v>-0.02886031124350059</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3437,10 +3437,10 @@
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.00272304329542059</v>
+        <v>-0.01775565247767849</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,52 +3449,52 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.02127749879792575</v>
+        <v>-0.01928960842925528</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.003156099246093989</v>
+        <v>-0.00934727829976254</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.03070151231558392</v>
+        <v>0.03427947121095878</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01668743870468487</v>
+        <v>0.05944244657730589</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.009385761317321925</v>
+        <v>0.0467897235921424</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01634200934975802</v>
+        <v>0.05855302085870747</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.01502080465482846</v>
+        <v>-0.004589397938460969</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01886919451460421</v>
+        <v>-0.06267506739003621</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.003372369068646319</v>
+        <v>-0.01676104395892386</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.00191791348596938</v>
+        <v>-0.004059916444691094</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.006707568031340302</v>
+        <v>0.03596595902548097</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,49 +3548,49 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.001584281138956051</v>
+        <v>-0.03686714714696952</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.004963156295146576</v>
+        <v>0.05407948197015771</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01076131083411386</v>
+        <v>0.03038871627173954</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.001347343237803925</v>
+        <v>-0.02097471826624766</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-7.070677795067652e-05</v>
+        <v>-0.008420426828291435</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.009066767743338254</v>
+        <v>0.02818362047132294</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3599,22 +3599,22 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.008095523122712152</v>
+        <v>-0.00636322001004334</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0002717469194852843</v>
+        <v>-0.001967975199518734</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.008653255255182639</v>
+        <v>0.008793988403927483</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,31 +3623,31 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.004643048325089712</v>
+        <v>-0.009124293953369436</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01611190074836967</v>
+        <v>-0.001795247996683495</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.001014505929216765</v>
+        <v>0.04370373794742251</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,73 +3656,73 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.007704291731332574</v>
+        <v>-0.01618082282570384</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.007215414713973275</v>
+        <v>-0.004158023514243391</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.005439830514608927</v>
+        <v>0.0182293996294674</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.002413293050505201</v>
+        <v>-0.02812929417170345</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.001542894305188213</v>
+        <v>-0.02869008607287273</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.008478916975591309</v>
+        <v>0.00102294773171085</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.002294994370496084</v>
+        <v>-0.003742161091632103</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01190800602009629</v>
+        <v>-0.008492661858234947</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03541540140571448</v>
+        <v>0.02597954842283718</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -3731,28 +3731,28 @@
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.00366400056016496</v>
+        <v>-0.02670418451923583</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.002399040335755978</v>
+        <v>-0.01819987338101251</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.0107308776449688</v>
+        <v>0.02485156048672463</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3761,10 +3761,10 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.006525487073643154</v>
+        <v>-0.02994241548326441</v>
       </c>
       <c r="FI6" t="n">
         <v>0</v>
@@ -3773,25 +3773,25 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01656149408850831</v>
+        <v>0.01673794546285282</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01926377877661225</v>
+        <v>-0.0131087535848409</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.003285774797124471</v>
+        <v>0.03268259890666899</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.002158901712802789</v>
+        <v>0.009202141563590359</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.003412779985610374</v>
+        <v>-0.03141402093749058</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,13 +3812,13 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02342710951493609</v>
+        <v>0.0169788150243026</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0008644342568427885</v>
+        <v>0.017914952349959</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1245170586821282</v>
+        <v>0.06674391054459913</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01727062703946451</v>
+        <v>-0.02398873480187061</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.410615090424475e-11</v>
+        <v>-1.194627137747305e-11</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07041758536805662</v>
+        <v>0.1136129358137827</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.07878680048788192</v>
+        <v>-0.03199198365588551</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0256039941057025</v>
+        <v>-0.002754915128315094</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01345014692042715</v>
+        <v>-0.006492641489548097</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,34 +3910,34 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.01199748571849331</v>
+        <v>-0.02179057828795061</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-3.286156406066523e-12</v>
+        <v>2.406577119693117e-13</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.05252679087646914</v>
+        <v>-0.03607013489367717</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.03927114641936681</v>
+        <v>-0.03075311370022917</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01744415924002832</v>
+        <v>-0.001397288356068034</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03902660757593394</v>
+        <v>0.0330046484028904</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.03280458829489486</v>
+        <v>-0.01266478449244862</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.02378383903235459</v>
+        <v>-0.02029725851112656</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1905849210809099</v>
+        <v>0.1230168179349194</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.08606747467014614</v>
+        <v>-0.01432419728201994</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,94 +4003,94 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.006354336289067467</v>
+        <v>0.01667326338145508</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.009215507838232221</v>
+        <v>-0.01377348678548385</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.07981757866051244</v>
+        <v>-0.03108687252119157</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.006496526001873809</v>
+        <v>-0.004317086978353366</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.02391548789790811</v>
+        <v>0.01930030103822132</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1167342020435507</v>
+        <v>0.05188031587119746</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.04186735348492758</v>
+        <v>0.01628391540138223</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1293541678976725</v>
+        <v>0.08573297567501686</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.01176170911050859</v>
+        <v>-0.03314239699569339</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.008628466612801509</v>
+        <v>-0.02085876607115564</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.03546687815670187</v>
+        <v>-0.03335379445576045</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0009509887705276528</v>
+        <v>0.008874111510886143</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,13 +4111,13 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0380250913166352</v>
+        <v>0.01788186087902744</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.01659763217467215</v>
+        <v>-0.03354345631346824</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
@@ -4126,10 +4126,10 @@
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.02549011768845449</v>
+        <v>0.006211807277424296</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.000930190420562084</v>
+        <v>0.02326816366166031</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.03280479973452971</v>
+        <v>-0.03491021095414136</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,34 +4153,34 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.005997996364432333</v>
+        <v>0.004274381160962643</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.03838702393791223</v>
+        <v>0.01676930956963543</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1249591797811167</v>
+        <v>-0.02571709088441206</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.03546545665076578</v>
+        <v>-0.007880009845948653</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4192,94 +4192,94 @@
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.02299922481168991</v>
+        <v>-0.009025773606800404</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.004233011607000322</v>
+        <v>-0.01432268334855208</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.009211699487474355</v>
+        <v>0.009202472665057103</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.00992348571587787</v>
+        <v>-0.02900692437673816</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.006025811196645231</v>
+        <v>0.01828364170778788</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.02335243297789449</v>
+        <v>-0.01197250472336839</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0.005629044866320155</v>
+        <v>-0.0003713612682822686</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.002614448165116416</v>
+        <v>-0.02844292692377244</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.02933836291557374</v>
+        <v>-0.0005655626301866182</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.03877296370443496</v>
+        <v>0.01072067266816899</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.05436425553919905</v>
+        <v>-0.008514605808965897</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.006765311659216708</v>
+        <v>-0.003645716793357002</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.01274444701028924</v>
+        <v>0.001920057917969657</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.04381703005391028</v>
+        <v>-0.0387827263423481</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.004579729314496992</v>
+        <v>-0.003029342256950758</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,67 +4327,67 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.02378788003243101</v>
+        <v>0.01682532996893707</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.05567570707103647</v>
+        <v>-0.02736542666512177</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02223183010824357</v>
+        <v>-0.001816913553291618</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.02079252262764474</v>
+        <v>0.06384152430947955</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.07428236867469985</v>
+        <v>0.02189500396532409</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.01856989979269897</v>
+        <v>-0.01930418766311728</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0001657178490216724</v>
+        <v>-0.0003048346687005741</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.05118978563357166</v>
+        <v>-0.01059521872989204</v>
       </c>
       <c r="GA7" t="n">
         <v>0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.04540791743623831</v>
+        <v>0.005381385024106648</v>
       </c>
     </row>
     <row r="8">
@@ -4985,16 +4985,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6543182288984134</v>
+        <v>0.1317058025695398</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2454052613929606</v>
+        <v>-0.09513926998493344</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.07050846786244298</v>
+        <v>-0.005466688364029427</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5009,19 +5009,19 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4770367269722562</v>
+        <v>0.1543852188328511</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2491339109266995</v>
+        <v>-0.1476742533587188</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1452453081668913</v>
+        <v>-0.04534681125942682</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5039,46 +5039,46 @@
         <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09566595643398519</v>
+        <v>0.04231215901643014</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.07393490199511957</v>
+        <v>-0.01318560134743363</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.08492032727707781</v>
+        <v>-0.03926957311676795</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.207624884915939</v>
+        <v>0.00814090795156735</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.05089021325272716</v>
+        <v>-0.07984977479350744</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.01632237761952453</v>
+        <v>-0.04586092451284551</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
         <v>-0</v>
@@ -5090,25 +5090,25 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1242579949471883</v>
+        <v>0.1234292775556806</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.1014526064781172</v>
+        <v>-0.100597402536493</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.1669429434542812</v>
+        <v>0.07107010514553684</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
@@ -5120,43 +5120,43 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.715078753976356</v>
+        <v>0.1638066207965212</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.05233798494163107</v>
+        <v>-0.09231998838072322</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1599099635676433</v>
+        <v>-0.1692046367632872</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0531365681812152</v>
+        <v>-0.05390726959223686</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.08745235867733951</v>
+        <v>-0.001779093174720392</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.284665504177408</v>
+        <v>0.004326005464842009</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.209260907843521</v>
+        <v>0.02713194937120544</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.08366408636441444</v>
+        <v>0.01294880698229509</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1630737788883857</v>
+        <v>0.01048857686251312</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,19 +5201,19 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.5057143204733496</v>
+        <v>0.1934405309694617</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.1165374453956266</v>
+        <v>-0.1756385387398286</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.0004625942301554815</v>
+        <v>-0.06289178213896504</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5228,19 +5228,19 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1923923997673583</v>
+        <v>-0.07504991044077694</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.04409052946038188</v>
+        <v>0.1154443713341765</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.05068964188686354</v>
+        <v>0.009115286537946014</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ9" t="n">
         <v>-0</v>
@@ -5249,82 +5249,82 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.02373354515003009</v>
+        <v>-0.05639818792939884</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1574384384121277</v>
+        <v>0.16943801653533</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1128264631353264</v>
+        <v>0.07608220880845093</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.1548701146981225</v>
+        <v>-0.05845275654865131</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.1013613079780224</v>
+        <v>0.1254300779629291</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.02193855104829247</v>
+        <v>0.02025431459882526</v>
       </c>
       <c r="DA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.02281959107999462</v>
+        <v>-0.001107543041578554</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.1354955765898423</v>
+        <v>0.01702190982431159</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.09352830715113057</v>
+        <v>-0.04833327429930966</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5333,25 +5333,25 @@
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.1124793352303008</v>
+        <v>-0.06721499578456157</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.02418091696712872</v>
+        <v>0.09111953484374034</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.0917672507813692</v>
+        <v>0.0002495167848614203</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,76 +5363,76 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.03416704574363146</v>
+        <v>0.04001110927731313</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.03066875350357114</v>
+        <v>0.03476640597178254</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.02469942060875089</v>
+        <v>-0.02136677668685479</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.07252052613720039</v>
+        <v>0.004903819069662271</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.04976611168744887</v>
+        <v>0.08298617898022749</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.06137540882260559</v>
+        <v>0.03630614507134587</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.1744042689161833</v>
+        <v>-0.04744506823997831</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.1082888934296245</v>
+        <v>-0.09576768941165703</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.07007926512395128</v>
+        <v>0.0009662936402379252</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,46 +5444,46 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.1592933864248273</v>
+        <v>-0.0760598573319602</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.08306958197710543</v>
+        <v>0.141510497569359</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.02804636499683423</v>
+        <v>0.003958326697565989</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.05459431824287222</v>
+        <v>-0.03805347287647933</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.1000888544170404</v>
+        <v>0.03126905377388346</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.05858219544902887</v>
+        <v>-0.04386537764319105</v>
       </c>
       <c r="FL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
@@ -5492,25 +5492,25 @@
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.05196896018357288</v>
+        <v>0.07103665638234316</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.06672268123162263</v>
+        <v>0.1335812988872047</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.03538622707356667</v>
+        <v>-0.1131861585236783</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
@@ -5522,16 +5522,16 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.04709241035432318</v>
+        <v>-0.01662829678154575</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.02943617802589304</v>
+        <v>0.04746302230852477</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
@@ -5543,10 +5543,10 @@
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>1.531575622847054</v>
+        <v>0.1962707008548212</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3035035916383439</v>
+        <v>-0.2209153121547096</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.03880238370640448</v>
+        <v>-0.06848988223269385</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,25 +5572,25 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.01335111260880942</v>
+        <v>-0.009293235024587532</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9551797552781358</v>
+        <v>0.167032470425927</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4137837530707054</v>
+        <v>-0.3480325254745559</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3793453029792817</v>
+        <v>-0.1464211328788806</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,133 +5599,133 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001874966297832298</v>
+        <v>0.0007855192766520939</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3502475606779367</v>
+        <v>0.09132672642001424</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2288679467389948</v>
+        <v>-0.06007016861743291</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1357098686172994</v>
+        <v>-0.1248165727875382</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-1.541093494189866e-10</v>
+        <v>2.93294234664993e-12</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.3097452210711173</v>
+        <v>-0.06151203154143967</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.01518780349784764</v>
+        <v>-0.06973209131100941</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.193087936411644</v>
+        <v>-0.1846763058934232</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.01133545403964669</v>
+        <v>0.02587493286895138</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1389008999186718</v>
+        <v>0.1752977955717658</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.2035750123615001</v>
+        <v>-0.05415577340294011</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.2718032052421592</v>
+        <v>0.08567220413028331</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.1432942661680622</v>
+        <v>0.02026719995641314</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.659168444614678</v>
+        <v>0.2051967747705423</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.03892165595474622</v>
+        <v>-0.1055201018394815</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.4659724973062234</v>
+        <v>-0.3542237939570581</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.3066557668129501</v>
+        <v>-0.02060246301429922</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.2374170934882057</v>
+        <v>-0.05115845863642994</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.2586506140884827</v>
+        <v>-0.08184087349999579</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.7483988788107312</v>
+        <v>-0.02005679312641787</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,34 +5734,34 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-7.851553063603998e-11</v>
+        <v>3.294812733210876e-11</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6579918986640476</v>
+        <v>0.01397148357175439</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.4399559283625533</v>
+        <v>0.1327535715320923</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.478559856120702</v>
+        <v>-0.05295216527751279</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.07729020654223265</v>
+        <v>-0.007905402710841244</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,70 +5770,70 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>1.052471888870448</v>
+        <v>0.2355136316986593</v>
       </c>
       <c r="BW10" t="n">
         <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.1237086035371414</v>
+        <v>-0.2480744331051697</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.1164186891900067</v>
+        <v>-0.2198335105190591</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0009499644208825615</v>
+        <v>-0.05733630680801859</v>
       </c>
       <c r="CC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.4208705522147348</v>
+        <v>-0.06530578332333498</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.03434232356979181</v>
+        <v>0.2075637705442269</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.115482615303064</v>
+        <v>0.0475509516153837</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0.04745418740933616</v>
+        <v>-0.04904294567350552</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.179683675816605</v>
+        <v>0.006889628011018774</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.2474318995594828</v>
+        <v>0.1347727487786529</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.1014319342180831</v>
+        <v>0.2507482441082096</v>
       </c>
       <c r="CR10" t="n">
         <v>0</v>
@@ -5842,61 +5842,61 @@
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.1066017584197897</v>
+        <v>0.03479434339335339</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.3057406967515879</v>
+        <v>-0.06581531002846951</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.1606741187939322</v>
+        <v>0.225712569657522</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.1700566288480446</v>
+        <v>0.06849767139425715</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0.04346460450210993</v>
+        <v>-0.03281589873270507</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.2431737952503816</v>
+        <v>-0.07063712585624031</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.07792466958625295</v>
+        <v>0.07569994522566106</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.003492118071903564</v>
+        <v>-0.0002835927348392921</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.03847894328686548</v>
+        <v>-0.05780995462551869</v>
       </c>
       <c r="DM10" t="n">
         <v>-0</v>
@@ -5905,70 +5905,70 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.2054781217661923</v>
+        <v>-0.04338000621783463</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.02844770409258144</v>
+        <v>0.1204801732005642</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.08172518465307367</v>
+        <v>-0.07538304740930218</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.2511386209705995</v>
+        <v>0.1291919286512503</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.1921276057874205</v>
+        <v>0.04863525568844617</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.06530732372956215</v>
+        <v>0.1211350581510343</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.4095713959521108</v>
+        <v>-0.09031367932136757</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC10" t="n">
         <v>0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.05887086000406132</v>
+        <v>0.1723286974825907</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.2729258655100302</v>
+        <v>0.04293039768413165</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0.01814653059834721</v>
+        <v>0.1419690284047548</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.004243777761490923</v>
+        <v>0.03792192635406318</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,7 +5977,7 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.02600096185906913</v>
+        <v>-0.04738574089097992</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
@@ -5986,133 +5986,133 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.3091174324415055</v>
+        <v>-0.06723014751635698</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.2225230300226121</v>
+        <v>0.196703371292869</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.3425725795509977</v>
+        <v>-0.01239800646967576</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.318291063748977</v>
+        <v>0.005673721092151988</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.3323601671121393</v>
+        <v>-0.0789174950636527</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.08846559432577611</v>
+        <v>0.2554363833307468</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.04382246201137208</v>
+        <v>0.06482746182373725</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0.05893173298448707</v>
+        <v>-0.04054490162531686</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.1355718019100721</v>
+        <v>-0.030217727444235</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.1604699685116748</v>
+        <v>-0.06490325723450383</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.121117392190496</v>
+        <v>0.0766301592611657</v>
       </c>
       <c r="FL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM10" t="n">
         <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.001602534119166642</v>
+        <v>-0.07982503433787502</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.4488850784772843</v>
+        <v>0.08825695041198471</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.3062427002878227</v>
+        <v>0.2326579613521945</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.4650825621738107</v>
+        <v>-0.1996672115624424</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.283717000712891</v>
+        <v>-0.1592506145929475</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.201437419299948</v>
+        <v>0.007799808469470785</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.1526121894849035</v>
+        <v>0.1109219837770839</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.1424059277992508</v>
+        <v>-0.06064042199717221</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6123,22 +6123,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2332134933879578</v>
+        <v>0.4337581425420718</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.03544179420758711</v>
+        <v>0.01526562029529208</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2400530494393987</v>
+        <v>-0.3708421270051875</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
@@ -6150,19 +6150,19 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1987251144504411</v>
+        <v>0.5919255815274341</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.05056407509386532</v>
+        <v>-0.1388825294718454</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.254682874659875</v>
+        <v>-0.4170582228564819</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03467117681937926</v>
+        <v>0.158228500771625</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,37 +6186,37 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.00202919686654925</v>
+        <v>-0.1487358303533841</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01164633955493513</v>
+        <v>-0.03975333067741553</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.04513573810946118</v>
+        <v>-0.001477343033744815</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01479164809285905</v>
+        <v>-0.3839409392603828</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.001309713828557884</v>
+        <v>-0.01327041528887791</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0401583989204484</v>
+        <v>0.1903390203862122</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.005340742034979272</v>
+        <v>-0.000754496334259445</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.05480123820107424</v>
+        <v>-0.09623019750841766</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,22 +6255,22 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.220563808934693</v>
+        <v>0.5672192949686201</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.02391979107662649</v>
+        <v>-0.2542062514470438</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.07379284313162224</v>
+        <v>-0.1630649931330341</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -6279,67 +6279,67 @@
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.09331923496617633</v>
+        <v>-0.05714048226308276</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1048640403036814</v>
+        <v>-0.07785340827117321</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.1447599157857291</v>
+        <v>-0.1403116809007851</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1418455940031909</v>
+        <v>0.1203694544728658</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0840472297757523</v>
+        <v>0.1093497810886922</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.01382281932415459</v>
+        <v>0.04350307064130512</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1256486563806616</v>
+        <v>0.4993961536739888</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.005770745469271098</v>
+        <v>-0.1192054050649948</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.04424447158273351</v>
+        <v>-0.2239689828437132</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6366,22 +6366,22 @@
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.05778444696850753</v>
+        <v>-0.2078335274409081</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.005188020618768652</v>
+        <v>0.003622359461334154</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.05921975239475136</v>
+        <v>0.154482741236059</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,19 +6393,19 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.0325321465586089</v>
+        <v>-0.2056453981222934</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.006546337467223458</v>
+        <v>0.18273484501169</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.0267339833339177</v>
+        <v>0.09843848064521764</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
@@ -6414,28 +6414,28 @@
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV11" t="n">
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.03701113695648368</v>
+        <v>-0.1755540084453491</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.00210469401672321</v>
+        <v>-0.006133975265750281</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.05801621785847292</v>
+        <v>0.1603571042038145</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
@@ -6444,10 +6444,10 @@
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.06467916589949237</v>
+        <v>-0.1024788634135377</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
@@ -6456,10 +6456,10 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.03609113386296669</v>
+        <v>-0.2042246341594059</v>
       </c>
       <c r="DJ11" t="n">
-        <v>-0.002820911883901143</v>
+        <v>0.009348828485793537</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,214 +6468,214 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.04143633505464896</v>
+        <v>-0.1085144734680599</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.02103675142362633</v>
+        <v>-0.01440150865969665</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.0160852879469403</v>
+        <v>0.04613512488366462</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.00123684261127811</v>
+        <v>0.06289335858954295</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.02531081575052967</v>
+        <v>0.03876121320037371</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.009240720354841796</v>
+        <v>0.1477360214470058</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.004732692751279164</v>
+        <v>-0.003400194784020837</v>
       </c>
       <c r="EH11" t="n">
         <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.002637836184552318</v>
+        <v>-0.09656070574301871</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.05082868573023527</v>
+        <v>0.1050501087455867</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.017528695752473</v>
+        <v>-0.07374252927460967</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.007591795309097581</v>
+        <v>-0.1458770304391638</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.05440216800615946</v>
+        <v>0.1161509922117894</v>
       </c>
       <c r="EU11" t="n">
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.03538202322432573</v>
+        <v>-0.2248762969347468</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.002171032440537826</v>
+        <v>-0.0209351119404597</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.06288410224842225</v>
+        <v>0.1379925253829755</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.02934258166379928</v>
+        <v>-0.2252961178160701</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.0230812351932118</v>
+        <v>0.1899293857209394</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03652020342362567</v>
+        <v>0.1278263541014132</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0005432634856441182</v>
+        <v>0.1699543135217781</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.04779573900838213</v>
+        <v>-0.02494101819446838</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.03962280391314596</v>
+        <v>0.1113872073897875</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.05956890083089189</v>
+        <v>-0.05609935330453256</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.03368527685343767</v>
+        <v>0.1141259178674744</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6692,16 +6692,16 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4896064756208952</v>
+        <v>0.443574478792379</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2309028801923033</v>
+        <v>-0.2139051396517936</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08305684167446767</v>
+        <v>-0.02385209503278557</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6719,16 +6719,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3771184643092149</v>
+        <v>0.4936829432838828</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2217467417972209</v>
+        <v>-0.3027008265621178</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1657725038647826</v>
+        <v>-0.113956205054061</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6737,109 +6737,109 @@
         <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1514495471127581</v>
+        <v>0.1077203894249732</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.02533807917614491</v>
+        <v>-0.06410357016776766</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.01149115641329817</v>
+        <v>-0.09289892675703225</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1685646122372646</v>
+        <v>-0.1170530106832654</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.005783715539000877</v>
+        <v>-0.1402374563506517</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.02774278678802661</v>
+        <v>-0.1373785635040874</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.094142529651131</v>
+        <v>0.1803190473073729</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.07197125697890189</v>
+        <v>-0.1261053707865959</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.09287561639270131</v>
+        <v>0.104502119523055</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.449988655398409</v>
+        <v>0.3004231531802788</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.03919735328449044</v>
+        <v>-0.1022662337785185</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.07953876210570165</v>
+        <v>-0.1864687206439853</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
         <v>-0</v>
@@ -6854,16 +6854,16 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.04143062651144329</v>
+        <v>-0.001050702583433357</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.101573390318132</v>
+        <v>-0.06322538501760762</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.2991556467980564</v>
+        <v>-0.04995673193415934</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1139217433462815</v>
+        <v>-0.02873182440868911</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.1320805763540848</v>
+        <v>0.03012692227550876</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.05254725485349346</v>
+        <v>0.0718926859937308</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,19 +6908,19 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2908355736057165</v>
+        <v>0.3328672414054169</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.06328912260933217</v>
+        <v>-0.1701263682619809</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.01749062430093183</v>
+        <v>-0.04674608760937146</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
@@ -6935,16 +6935,16 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1263924641525344</v>
+        <v>-0.1732913589178355</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.02768457033507683</v>
+        <v>0.1663227260307643</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01981898095853956</v>
+        <v>0.003586963676245608</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6956,106 +6956,106 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.01740565730966163</v>
+        <v>-0.05250405419514774</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.07546322297380918</v>
+        <v>0.2184328913575291</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.05070972909565125</v>
+        <v>0.053936378662546</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.09244459591766871</v>
+        <v>-0.1594567244584567</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.06372778039049073</v>
+        <v>0.1701293355222551</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.02503985164411303</v>
+        <v>0.02434210709687536</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.04027687466550523</v>
+        <v>-0.1264471765854707</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.04008456396513282</v>
+        <v>0.02889514782658465</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.004273033938194803</v>
+        <v>-0.1053849643103972</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN12" t="n">
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.05554651492820605</v>
+        <v>-0.1005603291995927</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.004025791734242228</v>
+        <v>0.09180459214298768</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.06824269948297181</v>
+        <v>-0.001780739831108044</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
@@ -7067,25 +7067,25 @@
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.01240828334058672</v>
+        <v>0.01614564911272179</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.02795782960921392</v>
+        <v>-0.07381511957983826</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.01501967967656154</v>
+        <v>0.03393799835513487</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
@@ -7097,49 +7097,49 @@
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.05745877501571076</v>
+        <v>-0.1014570888573106</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.08090235799642295</v>
+        <v>0.1403845658546515</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.05345401525280432</v>
+        <v>0.03994036694536478</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.0951908767739568</v>
+        <v>-0.1073369838426457</v>
       </c>
       <c r="EQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.07941046388922951</v>
+        <v>0.1005894468781808</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.01546908025777557</v>
+        <v>-0.04473636550806701</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,46 +7151,46 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.09888292185145392</v>
+        <v>-0.1824202382277149</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.06765186331558917</v>
+        <v>0.1946763197419414</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.02020214186556918</v>
+        <v>-0.009852728381715973</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.02176354429448201</v>
+        <v>-0.1311879897930352</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.07960796045175664</v>
+        <v>0.09105399941172043</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.04367884813112553</v>
+        <v>-0.001458270363483956</v>
       </c>
       <c r="FL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
@@ -7199,25 +7199,25 @@
         <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.006567479633126588</v>
+        <v>0.02090042053130046</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.02453349919864233</v>
+        <v>0.1960056074292884</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01375657060832267</v>
+        <v>0.02040178718749502</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
@@ -7226,42 +7226,42 @@
         <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.007896691870030408</v>
+        <v>-0.1378605967519991</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.03652229951168325</v>
+        <v>0.1164118794652583</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.4038779656272438</v>
+        <v>-0.1534961208103207</v>
       </c>
       <c r="C13" t="n">
         <v>-0</v>
@@ -7270,10 +7270,10 @@
         <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.252940822526486</v>
+        <v>-0.00621157420360221</v>
       </c>
       <c r="F13" t="n">
-        <v>1.004293458228433</v>
+        <v>0.2599389458942493</v>
       </c>
       <c r="G13" t="n">
         <v>-0</v>
@@ -7285,22 +7285,22 @@
         <v>-0</v>
       </c>
       <c r="J13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.35082889039237</v>
+        <v>-0.1833147592088506</v>
       </c>
       <c r="L13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0456529205747749</v>
+        <v>0.0669483068440066</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9486198483704671</v>
+        <v>0.2566602908209205</v>
       </c>
       <c r="P13" t="n">
         <v>-0</v>
@@ -7315,46 +7315,46 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.007323211930176531</v>
+        <v>-0.1019102520178801</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>-0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3648031684274533</v>
+        <v>0.1187723964580319</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1476500601528246</v>
+        <v>0.03005030745915289</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.007262553587481343</v>
+        <v>0.02415067739866929</v>
       </c>
       <c r="AD13" t="n">
         <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.08842377121394167</v>
+        <v>0.2385278365953732</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.1192495607529106</v>
+        <v>0.1522975328758793</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,28 +7363,28 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
         <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.05543900485881876</v>
+        <v>-0.09411074535628275</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
         <v>-0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.05540884590526624</v>
+        <v>-0.05590713259463718</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.1360647849376689</v>
+        <v>0.106726612493951</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -7393,22 +7393,22 @@
         <v>-0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0.2456124845371395</v>
+        <v>-0.2452981940855559</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.3421987864202187</v>
+        <v>0.05171414417084679</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.6302369896101782</v>
+        <v>0.09338440125220736</v>
       </c>
       <c r="AZ13" t="n">
         <v>-0</v>
@@ -7417,13 +7417,13 @@
         <v>-0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>-0.2548358148685912</v>
+        <v>0.07230129232529935</v>
       </c>
       <c r="BE13" t="n">
         <v>-0</v>
@@ -7432,37 +7432,37 @@
         <v>-0</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0218438821155179</v>
+        <v>0.1889780757483696</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.2968843695086321</v>
+        <v>0.157165976884677</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
         <v>0</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0.1807245679610263</v>
+        <v>0.009281956524180427</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.0376486874184526</v>
+        <v>-0.07756745417509329</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01328882608151478</v>
+        <v>-0.02183278040319565</v>
       </c>
       <c r="BR13" t="n">
         <v>-0</v>
@@ -7471,31 +7471,31 @@
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0.2462451899738088</v>
+        <v>-0.2374428819048555</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX13" t="n">
         <v>-0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.2647256661989952</v>
+        <v>0.04157653177968147</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.527206857049178</v>
+        <v>0.1680041774802466</v>
       </c>
       <c r="CA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC13" t="n">
         <v>-0</v>
@@ -7504,49 +7504,49 @@
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.08447725089768096</v>
+        <v>0.07941038526247665</v>
       </c>
       <c r="CF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG13" t="n">
         <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.06434347419159975</v>
+        <v>-0.02320866108464563</v>
       </c>
       <c r="CI13" t="n">
-        <v>-0.2316991681850791</v>
+        <v>-0.09678259768103831</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM13" t="n">
         <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.001638102472490346</v>
+        <v>0.09879870544844777</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
         <v>0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.185656862387951</v>
+        <v>-0.1984289809147696</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.04180492059408605</v>
+        <v>-0.1033954043292534</v>
       </c>
       <c r="CS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT13" t="n">
         <v>0</v>
@@ -7558,22 +7558,22 @@
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.06305996825655596</v>
+        <v>0.07451021568290667</v>
       </c>
       <c r="CX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY13" t="n">
         <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.07296972230142253</v>
+        <v>-0.02170266770939826</v>
       </c>
       <c r="DA13" t="n">
-        <v>-0.2277076493561072</v>
+        <v>-0.08990481438157355</v>
       </c>
       <c r="DB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
@@ -7585,46 +7585,46 @@
         <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.0144655441839394</v>
+        <v>0.03991128053262398</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.173822266938652</v>
+        <v>0.09235054604193343</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.04429230440509047</v>
+        <v>-0.01532210695927314</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.071168355887666</v>
+        <v>0.04953649872275274</v>
       </c>
       <c r="DP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.119166323047539</v>
+        <v>0.01395857075713058</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.1067744411414192</v>
+        <v>-0.06869232907007741</v>
       </c>
       <c r="DT13" t="n">
         <v>0</v>
@@ -7636,49 +7636,49 @@
         <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.068564282564954</v>
+        <v>-0.03014031437526173</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.08325850587336775</v>
+        <v>0.04326848274074811</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.146120686586263</v>
+        <v>-0.0409995119374324</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.1140250382198324</v>
+        <v>0.02840247553242475</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
         <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.1275624402340746</v>
+        <v>0.01831114580890502</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0.1873279686156629</v>
+        <v>-0.03891159113441683</v>
       </c>
       <c r="EL13" t="n">
         <v>0</v>
@@ -7687,28 +7687,28 @@
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.02317844835887528</v>
+        <v>0.01126504819429732</v>
       </c>
       <c r="EQ13" t="n">
         <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.06519178837433443</v>
+        <v>0.03096063155811453</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0.1277610607903486</v>
+        <v>-0.06219154261881416</v>
       </c>
       <c r="EU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV13" t="n">
         <v>-0</v>
@@ -7717,25 +7717,25 @@
         <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.06173667903328039</v>
+        <v>0.08857507682717025</v>
       </c>
       <c r="EZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA13" t="n">
         <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.1325270370104459</v>
+        <v>-0.01925724955752789</v>
       </c>
       <c r="FC13" t="n">
-        <v>-0.2097606973381144</v>
+        <v>-0.09023338707966752</v>
       </c>
       <c r="FD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
@@ -7747,7 +7747,7 @@
         <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.06555520408405964</v>
+        <v>0.1140443711481865</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,25 +7756,25 @@
         <v>0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.08483116572936242</v>
+        <v>-0.05460727867039493</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0462952873793121</v>
+        <v>0.04785448910866768</v>
       </c>
       <c r="FM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP13" t="n">
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.04434455247705738</v>
+        <v>-0.03222682688134598</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
@@ -7783,10 +7783,10 @@
         <v>0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.2293599955196605</v>
+        <v>-0.01359186742144877</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.05722675267057771</v>
+        <v>0.05721434014587536</v>
       </c>
       <c r="FV13" t="n">
         <v>0</v>
@@ -7795,31 +7795,31 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.05345951618917034</v>
+        <v>0.0610597234177257</v>
       </c>
       <c r="GA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
         <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.006450741157154226</v>
+        <v>-0.009690206800755351</v>
       </c>
       <c r="GE13" t="n">
         <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>-0</v>
@@ -7827,7 +7827,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.2644734543839846</v>
+        <v>0.147432141916589</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -7836,25 +7836,25 @@
         <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1947782831286061</v>
+        <v>-0.2590449896664112</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1671644348028725</v>
+        <v>0.1110852209935956</v>
       </c>
       <c r="F14" t="n">
         <v>-0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
         <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2938076692936429</v>
+        <v>0.1029950979053732</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -7863,25 +7863,25 @@
         <v>-0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.08577461176398686</v>
+        <v>-0.3520202866749801</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1017940581280179</v>
+        <v>0.06801425234652334</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.05076803041991047</v>
+        <v>-0.0165766434280946</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -7890,40 +7890,40 @@
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1172659853958707</v>
+        <v>-0.05104600792590085</v>
       </c>
       <c r="W14" t="n">
-        <v>0.09223618383499266</v>
+        <v>-0.07630620717634011</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>-0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.08052758829533892</v>
+        <v>0.04981804211301129</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.04461024431856998</v>
+        <v>0.06415928986910852</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.036601401698017</v>
+        <v>0.1900113586374863</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -7932,49 +7932,49 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.0244040841119672</v>
+        <v>0.03933486705072187</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.02198507996598279</v>
+        <v>-0.1398890587052424</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.06874553309499501</v>
+        <v>0.04854102597738599</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
         <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.1190428792976139</v>
+        <v>-0.06877246111599114</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.04390090374942773</v>
+        <v>-0.2698061185866981</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.1862621093376844</v>
+        <v>-0.01848144728022177</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
@@ -7989,7 +7989,7 @@
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.225583641681062</v>
+        <v>0.178133613102284</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -7998,37 +7998,37 @@
         <v>-0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.01824311579764173</v>
+        <v>0.2217261543729907</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0689647680612504</v>
+        <v>0.1890265128226897</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.07697478273003901</v>
+        <v>-0.0144793739481669</v>
       </c>
       <c r="BM14" t="n">
         <v>0</v>
       </c>
       <c r="BN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.03494282299929821</v>
+        <v>0.01032879379483595</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.162093032367576</v>
+        <v>-0.1125419554963639</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
@@ -8037,25 +8037,25 @@
         <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.08010198631705157</v>
+        <v>-0.07034807069075093</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.01084659754069752</v>
+        <v>-0.2820230530760467</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.1446953566179339</v>
+        <v>-0.05898849161871091</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -8064,13 +8064,13 @@
         <v>0</v>
       </c>
       <c r="CB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0.04510280511768187</v>
+        <v>-0.06245154911102711</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
@@ -8079,16 +8079,16 @@
         <v>0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.01992012597227296</v>
+        <v>0.1112067071353654</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.04610688845684497</v>
+        <v>-0.03319881138051899</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
@@ -8097,34 +8097,34 @@
         <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0.06613730423390181</v>
+        <v>0.01045861803644514</v>
       </c>
       <c r="CN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.1630869772532761</v>
+        <v>0.1380363107661151</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.1453553463199664</v>
+        <v>-0.05454045770985184</v>
       </c>
       <c r="CR14" t="n">
         <v>0</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
         <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0.02759707254027938</v>
+        <v>-0.05361032585778481</v>
       </c>
       <c r="CW14" t="n">
         <v>-0</v>
@@ -8133,16 +8133,16 @@
         <v>-0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.008119419753870698</v>
+        <v>0.1148368770486763</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.03548651615657572</v>
+        <v>-0.01839097534394491</v>
       </c>
       <c r="DA14" t="n">
         <v>-0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>-0</v>
@@ -8151,7 +8151,7 @@
         <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0.02976916052095906</v>
+        <v>-0.01369696848266489</v>
       </c>
       <c r="DF14" t="n">
         <v>-0</v>
@@ -8160,10 +8160,10 @@
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.1015718723951174</v>
+        <v>0.1111953792507972</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.04777762138342724</v>
+        <v>-0.01322410193925079</v>
       </c>
       <c r="DJ14" t="n">
         <v>0</v>
@@ -8178,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0.04324590238342792</v>
+        <v>-0.06953240870907205</v>
       </c>
       <c r="DO14" t="n">
         <v>-0</v>
@@ -8187,70 +8187,70 @@
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.06840419933344914</v>
+        <v>0.01179963023274499</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.1169450445450007</v>
+        <v>-0.0007972962714696833</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0.07777727516968662</v>
+        <v>0.007763039466505312</v>
       </c>
       <c r="DX14" t="n">
         <v>-0</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.02959441468166746</v>
+        <v>0.01770560477130695</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.07574349818772393</v>
+        <v>0.004155388163913429</v>
       </c>
       <c r="EB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0.05109372526325343</v>
+        <v>-0.1028777196365567</v>
       </c>
       <c r="EG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.03547122038128789</v>
+        <v>0.09430375955150877</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.01696104452855</v>
+        <v>0.009249433245699623</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
@@ -8259,22 +8259,22 @@
         <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.004630800288238325</v>
+        <v>0.03411424276872299</v>
       </c>
       <c r="EP14" t="n">
         <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.04292069272040559</v>
+        <v>0.1262544066052814</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.005501907464312109</v>
+        <v>0.00889446127804136</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
         <v>0</v>
@@ -8286,34 +8286,34 @@
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0.03272245199866606</v>
+        <v>-0.06013721999780509</v>
       </c>
       <c r="EY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.009908774641307407</v>
+        <v>0.1496509629726257</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.04678307006786014</v>
+        <v>-0.02378819332530765</v>
       </c>
       <c r="FC14" t="n">
         <v>0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0.03680595171142252</v>
+        <v>0.02494042055040486</v>
       </c>
       <c r="FH14" t="n">
         <v>0</v>
@@ -8322,61 +8322,61 @@
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.02242446753442422</v>
+        <v>0.111565380538709</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.1962660321363101</v>
+        <v>0.1158607656155108</v>
       </c>
       <c r="FL14" t="n">
         <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
         <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.008351763273811654</v>
+        <v>-0.008050238098538574</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR14" t="n">
         <v>-0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.005768158845092641</v>
+        <v>0.2484758248660398</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.07394564231949566</v>
+        <v>0.05470237127513316</v>
       </c>
       <c r="FU14" t="n">
         <v>0</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
         <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.03694643230828373</v>
+        <v>0.02372834282140114</v>
       </c>
       <c r="FZ14" t="n">
         <v>0</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.05893067217737761</v>
+        <v>0.1906873344897305</v>
       </c>
       <c r="GC14" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
         <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -9537,25 +9537,25 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.7065178604482224</v>
+        <v>0.2528201304535646</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3251142847225449</v>
+        <v>-0.220450924785277</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.04111540132472373</v>
+        <v>-0.01254122486886844</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -9564,22 +9564,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5037354850863311</v>
+        <v>0.2778747219620277</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3681903566895708</v>
+        <v>-0.3208961712826739</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.06251627781253863</v>
+        <v>-0.0853988765490107</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -9591,79 +9591,79 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1429025858524632</v>
+        <v>0.04592348838461178</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.005480828142311104</v>
+        <v>-0.05660055794870787</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1705670371893918</v>
+        <v>-0.07188023918639294</v>
       </c>
       <c r="X17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.08339421472717569</v>
+        <v>-0.07023863220271982</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.01957105448551286</v>
+        <v>-0.1062538502081644</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.0884313639750423</v>
+        <v>-0.081471763373372</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.0004323416157562067</v>
+        <v>0.09040404957985654</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.08268058673765899</v>
+        <v>-0.1133141417839031</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01241979546189361</v>
+        <v>0.03457177809183355</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
@@ -9672,52 +9672,52 @@
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.4439040117196943</v>
+        <v>0.1795772343271506</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.03421995425815551</v>
+        <v>-0.03374633835224559</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.1507905290759396</v>
+        <v>-0.1302502960159083</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>-0</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.09882878396016453</v>
+        <v>-0.006680306094837624</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.2640365586448582</v>
+        <v>-0.04692592899359955</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.209210938208003</v>
+        <v>-0.008057280149080243</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -9726,16 +9726,16 @@
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.1657072666352129</v>
+        <v>0.01457973010241025</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.01435782810858063</v>
+        <v>0.06654243541484914</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.2456606896474722</v>
+        <v>0.04910076903443728</v>
       </c>
       <c r="BQ17" t="n">
         <v>-0</v>
@@ -9747,31 +9747,31 @@
         <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.2606967032568218</v>
+        <v>0.1695964564215532</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.04805953394859109</v>
+        <v>-0.1472603742556305</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.1480353059352174</v>
+        <v>-0.02783142879737721</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
@@ -9780,22 +9780,22 @@
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.1406986329679999</v>
+        <v>-0.07024873895011992</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.01008480351141594</v>
+        <v>0.1119961482713408</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.02705904532105713</v>
+        <v>0.007888747147629794</v>
       </c>
       <c r="CI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
@@ -9807,19 +9807,19 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.03216659555159981</v>
+        <v>-0.05676891984139141</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.2869574122163829</v>
+        <v>0.1933064464944833</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.1411724751987646</v>
+        <v>0.05115452688696653</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
@@ -9828,22 +9828,22 @@
         <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.1026822483072986</v>
+        <v>-0.06839786861448734</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.05992378437185925</v>
+        <v>0.1143621717064222</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.04180779933237944</v>
+        <v>0.02197608516857833</v>
       </c>
       <c r="DA17" t="n">
         <v>0</v>
@@ -9855,22 +9855,22 @@
         <v>-0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.03589188773824366</v>
+        <v>-0.05824391304558157</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.1093258869418087</v>
+        <v>0.03949582994121573</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.01443463975870397</v>
+        <v>-0.08585122403255427</v>
       </c>
       <c r="DJ17" t="n">
         <v>-0</v>
@@ -9885,28 +9885,28 @@
         <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.07713718915759761</v>
+        <v>-0.05590862366960447</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0.007024938210041608</v>
+        <v>-0.03101685643930682</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.06419543250611555</v>
+        <v>0.003734391596367094</v>
       </c>
       <c r="DS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
         <v>0</v>
@@ -9915,73 +9915,73 @@
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.06422371405277154</v>
+        <v>0.01382157378850465</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0.03961216787784566</v>
+        <v>0.08491225895530499</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.05366945409950179</v>
+        <v>-0.06349039387620901</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.1190824573759829</v>
+        <v>-0.04209490353908788</v>
       </c>
       <c r="EH17" t="n">
         <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>-0.004533356327923561</v>
+        <v>0.07394026376622519</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.1010724192287575</v>
+        <v>0.05737681836457516</v>
       </c>
       <c r="EK17" t="n">
         <v>0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.001357583644309067</v>
+        <v>-0.008645832463563229</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.01323821563639857</v>
+        <v>0.0746608563456978</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.0203614326946022</v>
+        <v>-0.03339430519551555</v>
       </c>
       <c r="ET17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU17" t="n">
         <v>0</v>
@@ -9996,25 +9996,25 @@
         <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.09999088069364616</v>
+        <v>-0.07638306983526327</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.001908397541044842</v>
+        <v>0.136969902930858</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.0007734146704566939</v>
+        <v>8.689639573875965e-05</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF17" t="n">
         <v>0</v>
@@ -10023,16 +10023,16 @@
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.007671948013946907</v>
+        <v>0.1087036038542414</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.03342994177197955</v>
+        <v>0.08010163120150732</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.004077968148340804</v>
+        <v>-0.03574131912494715</v>
       </c>
       <c r="FL17" t="n">
         <v>-0</v>
@@ -10044,52 +10044,52 @@
         <v>-0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.04114280749045465</v>
+        <v>0.04357007079266849</v>
       </c>
       <c r="FR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS17" t="n">
-        <v>3.913080121260596e-05</v>
+        <v>0.1433198072799721</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.04632459381955821</v>
+        <v>-0.0297180750896814</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
         <v>0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.08546176442438072</v>
+        <v>-0.002975258056249424</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.1374859100864664</v>
+        <v>0.04598843938639777</v>
       </c>
       <c r="GC17" t="n">
         <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
@@ -10106,22 +10106,22 @@
         <v>-0</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.5619917000709082</v>
+        <v>-0.1985471767258492</v>
       </c>
       <c r="C18" t="n">
         <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1530472642227293</v>
+        <v>0.1295297825269775</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9362792605459417</v>
+        <v>0.3781038327129465</v>
       </c>
       <c r="G18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10133,7 +10133,7 @@
         <v>-0</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4767687871084273</v>
+        <v>-0.2413086944884059</v>
       </c>
       <c r="L18" t="n">
         <v>-0</v>
@@ -10142,25 +10142,25 @@
         <v>-0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.04122978365678961</v>
+        <v>0.147578739935371</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8433122972362085</v>
+        <v>0.5026077135808263</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0475432154337135</v>
+        <v>-0.08610474146614432</v>
       </c>
       <c r="U18" t="n">
         <v>-0</v>
@@ -10169,37 +10169,37 @@
         <v>-0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2050281532278205</v>
+        <v>0.1229434905653386</v>
       </c>
       <c r="X18" t="n">
-        <v>0.09907608554540934</v>
+        <v>0.05548305601839743</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>-0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.002977187000966503</v>
+        <v>0.01738441493181222</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>-0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.06726947787242823</v>
+        <v>0.2534731061307202</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.08177119161255048</v>
+        <v>0.05677669509663089</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -10208,13 +10208,13 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK18" t="n">
         <v>-0</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.05516718054966616</v>
+        <v>-0.02841798499553655</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
@@ -10223,10 +10223,10 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.04480939744564025</v>
+        <v>0.02382389397362096</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.1585567645630519</v>
+        <v>0.02801971995493124</v>
       </c>
       <c r="AQ18" t="n">
         <v>0</v>
@@ -10238,25 +10238,25 @@
         <v>-0</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU18" t="n">
-        <v>-0.1148510245735235</v>
+        <v>-0.1129457872284865</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.183036517048427</v>
+        <v>0.05930502853034628</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.5286702026406493</v>
+        <v>0.2711721965407827</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
         <v>0</v>
@@ -10265,106 +10265,106 @@
         <v>-0</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD18" t="n">
-        <v>-0.2315018471534227</v>
+        <v>0.05599926823910134</v>
       </c>
       <c r="BE18" t="n">
         <v>-0</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.04568663868520217</v>
+        <v>0.09612413385737685</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.1582085733549655</v>
+        <v>0.009550721242951893</v>
       </c>
       <c r="BI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
         <v>0</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM18" t="n">
-        <v>-0.2294522057584735</v>
+        <v>-0.07967116897682239</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>-0.1167199057440235</v>
+        <v>-0.1307409766409288</v>
       </c>
       <c r="BQ18" t="n">
-        <v>-0.05162159786543732</v>
+        <v>-0.008827692196685633</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>-0.2825745575205455</v>
+        <v>-0.2023343343010711</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.1364092284791431</v>
+        <v>0.03987676978205441</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.2900536719343655</v>
+        <v>0.1859422709390816</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB18" t="n">
         <v>0</v>
       </c>
       <c r="CC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.1294144681169203</v>
+        <v>0.04787113007288958</v>
       </c>
       <c r="CF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG18" t="n">
         <v>0</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.04348271720928615</v>
+        <v>-0.05148792062005035</v>
       </c>
       <c r="CI18" t="n">
-        <v>-0.1900627142028209</v>
+        <v>-0.1085319935314834</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK18" t="n">
         <v>-0</v>
@@ -10373,91 +10373,91 @@
         <v>-0</v>
       </c>
       <c r="CM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.02601519506793283</v>
+        <v>0.1103535738804708</v>
       </c>
       <c r="CO18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP18" t="n">
         <v>0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.1410933516439072</v>
+        <v>-0.08408866474358222</v>
       </c>
       <c r="CR18" t="n">
-        <v>0.05349129152857736</v>
+        <v>-0.08267496578276527</v>
       </c>
       <c r="CS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU18" t="n">
         <v>0</v>
       </c>
       <c r="CV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW18" t="n">
-        <v>0.09015077542634586</v>
+        <v>0.04214291353679265</v>
       </c>
       <c r="CX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY18" t="n">
         <v>-0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.03522689207834725</v>
+        <v>-0.06516978710619777</v>
       </c>
       <c r="DA18" t="n">
-        <v>-0.1847526977996348</v>
+        <v>-0.133036224998893</v>
       </c>
       <c r="DB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC18" t="n">
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.0655835721812028</v>
+        <v>0.03545622004171077</v>
       </c>
       <c r="DG18" t="n">
         <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.1113462793900101</v>
+        <v>0.08102800015608212</v>
       </c>
       <c r="DJ18" t="n">
-        <v>-0.002143905054196045</v>
+        <v>-0.06052324931524088</v>
       </c>
       <c r="DK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN18" t="n">
         <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.04633259607907098</v>
+        <v>-0.08489054487313716</v>
       </c>
       <c r="DP18" t="n">
         <v>-0</v>
@@ -10466,37 +10466,37 @@
         <v>-0</v>
       </c>
       <c r="DR18" t="n">
-        <v>-0.1013827511756108</v>
+        <v>0.08203083593145243</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.01532740530663834</v>
+        <v>-0.01097860987653667</v>
       </c>
       <c r="DT18" t="n">
         <v>0</v>
       </c>
       <c r="DU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.1090447202370523</v>
+        <v>0.08301951954305971</v>
       </c>
       <c r="DY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ18" t="n">
         <v>0</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.05455194501742738</v>
+        <v>0.07819232414080643</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0.1630909021609638</v>
+        <v>-0.05683628690651318</v>
       </c>
       <c r="EC18" t="n">
         <v>0</v>
@@ -10505,28 +10505,28 @@
         <v>-0</v>
       </c>
       <c r="EE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG18" t="n">
-        <v>0.08762073590193339</v>
+        <v>0.03579441579756011</v>
       </c>
       <c r="EH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI18" t="n">
         <v>-0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>-0.05289292561205562</v>
+        <v>-0.07109954787038331</v>
       </c>
       <c r="EK18" t="n">
-        <v>-0.1737878300676208</v>
+        <v>-0.01670269649721539</v>
       </c>
       <c r="EL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM18" t="n">
         <v>0</v>
@@ -10535,55 +10535,55 @@
         <v>-0</v>
       </c>
       <c r="EO18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.02486131961238406</v>
+        <v>0.01021285194744568</v>
       </c>
       <c r="EQ18" t="n">
         <v>0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>-0.04217865694211088</v>
+        <v>-0.09479631555672173</v>
       </c>
       <c r="ET18" t="n">
-        <v>-0.03967402906449406</v>
+        <v>-0.1686777065184945</v>
       </c>
       <c r="EU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV18" t="n">
         <v>-0</v>
       </c>
       <c r="EW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY18" t="n">
-        <v>0.07601944216487953</v>
+        <v>0.06179372245155543</v>
       </c>
       <c r="EZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA18" t="n">
         <v>0</v>
       </c>
       <c r="FB18" t="n">
-        <v>-0.07794920266017073</v>
+        <v>-0.03314517235924489</v>
       </c>
       <c r="FC18" t="n">
-        <v>-0.1869361903526315</v>
+        <v>-0.1068723156671087</v>
       </c>
       <c r="FD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF18" t="n">
         <v>0</v>
@@ -10592,25 +10592,25 @@
         <v>-0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.002895793637364487</v>
+        <v>-0.09227654498347858</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
         <v>0</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.01024344760432382</v>
+        <v>0.07981970483048791</v>
       </c>
       <c r="FL18" t="n">
-        <v>-0.07917485854407756</v>
+        <v>-0.1198719740072357</v>
       </c>
       <c r="FM18" t="n">
         <v>-0</v>
       </c>
       <c r="FN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO18" t="n">
         <v>-0</v>
@@ -10619,46 +10619,46 @@
         <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>0.01301892063392341</v>
+        <v>-0.02421685682717587</v>
       </c>
       <c r="FR18" t="n">
         <v>0</v>
       </c>
       <c r="FS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.1341425293712213</v>
+        <v>0.1582420390534882</v>
       </c>
       <c r="FU18" t="n">
-        <v>-0.08341851681517694</v>
+        <v>0.04799749443041189</v>
       </c>
       <c r="FV18" t="n">
         <v>0</v>
       </c>
       <c r="FW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.08249638631278741</v>
+        <v>0.06229682121132786</v>
       </c>
       <c r="GA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB18" t="n">
         <v>0</v>
       </c>
       <c r="GC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD18" t="n">
-        <v>0.06682642202701633</v>
+        <v>-0.05467881809846119</v>
       </c>
       <c r="GE18" t="n">
         <v>0</v>
